--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>0.039</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="19">
@@ -1292,7 +1292,7 @@
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +889 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,64 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +820 €/mois.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/07/2026</t>
+          <t>Dossier généré le 07/07/2026</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>0.0464</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="19">
@@ -1292,7 +1292,7 @@
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,64 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +820 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +889 €/mois.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/07/2026</t>
+          <t>Dossier généré le 06/07/2026</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>0.039</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="19">
@@ -1292,7 +1292,7 @@
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +889 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,64 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +820 €/mois.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/07/2026</t>
+          <t>Dossier généré le 07/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/07/2026</t>
+          <t>Dossier généré le 08/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/07/2026</t>
+          <t>Dossier généré le 09/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/07/2026</t>
+          <t>Dossier généré le 10/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/07/2026</t>
+          <t>Dossier généré le 11/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>0.0464</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="19">
@@ -1292,7 +1292,7 @@
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,64 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +820 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +826 €/mois.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/07/2026</t>
+          <t>Dossier généré le 12/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -917,12 +917,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>3 000 à 6 500 €/m²</t>
+          <t>6 858 à 14 091 €/m²</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>ce bien est 4 % SOUS la médiane locale</t>
+          <t>ce bien est 59 % SOUS la médiane locale</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>Prix cohérent avec le marché local.</t>
+          <t>Décote sans explication visible dans l'annonce : possible bonne affaire — ou défaut caché (état, copropriété, bail) à vérifier sur place.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/07/2026</t>
+          <t>Dossier généré le 13/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Annonce" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0&quot; €/mois&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,12 +38,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001D5240"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="17"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -74,16 +74,23 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <color rgb="0098351B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001D5240"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
       <i val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0098351B"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <b val="1"/>
@@ -93,7 +100,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +110,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001D5240"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6A532"/>
       </patternFill>
     </fill>
     <fill>
@@ -128,46 +140,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment indent="1"/>
+      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -288,18 +307,21 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1D5240"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Synthèse'!$E$6:$E$8</f>
+              <f>'Synthèse'!$E$7:$E$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Synthèse'!$F$6:$F$8</f>
+              <f>'Synthèse'!$F$7:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -362,7 +384,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="1D5240"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -439,7 +464,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="2880000"/>
@@ -774,9 +799,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -784,542 +809,625 @@
     <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dossier de financement — Murs commerciaux</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Vente Local commercial 44m² Paris</t>
-        </is>
-      </c>
+          <t>Les Murs.   Dossier de financement — murs commerciaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="3" customHeight="1">
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Paris 6e (75006) — annonce cessionpme du 2026-07-03</t>
+          <t>Vente Local commercial 44m² Paris</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Voir l'annonce en ligne</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Dossier généré le 13/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+          <t>Paris 6e (75006) — annonce cessionpme du 2026-07-03</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Voir l'annonce en ligne ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Dossier généré le 13/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>L'ESSENTIEL — ce que votre conseiller lit en premier</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Loyer mensuel</t>
+        </is>
+      </c>
+      <c r="F7" s="8">
+        <f>IFERROR(B20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Prix d'achat retenu</t>
+        </is>
+      </c>
+      <c r="B8" s="10">
+        <f>B25</f>
+        <v/>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Crédit + charges / mois</t>
+        </is>
+      </c>
+      <c r="F8" s="8">
+        <f>B38-(B43+B44+B45)/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Apport nécessaire</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <f>B36</f>
+        <v/>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Cash-flow</t>
+        </is>
+      </c>
+      <c r="F9" s="8">
+        <f>B49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Mensualité de crédit estimée</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>B38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Cash-flow mensuel attendu</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>B49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>DSCR (≥ 1,20 rassure)</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>B54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +826 €/mois.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>LE BIEN</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Loyer mensuel</t>
-        </is>
-      </c>
-      <c r="F6" s="7">
-        <f>IFERROR(B11,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>État locatif</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Murs libres — local à louer après l'achat</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Crédit + charges / mois</t>
-        </is>
-      </c>
-      <c r="F7" s="7">
-        <f>B28-(B33+B34+B35)/12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B17" s="16" t="n">
         <v>44</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Cash-flow</t>
-        </is>
-      </c>
-      <c r="F8" s="7">
-        <f>B39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Prix affiché</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B18" s="17" t="n">
         <v>200000</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Prix au m²</t>
         </is>
       </c>
-      <c r="B10" s="11">
-        <f>IFERROR(B9/B8,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B19" s="17">
+        <f>IFERROR(B18/B17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Loyer mensuel HT</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B20" s="17" t="n">
         <v>2252</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>loyer du bail en place (à faire confirmer par le bail)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Marché local (prix/m²)</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>6 858 à 14 091 €/m²</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>ce bien est 59 % SOUS la médiane locale</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Source de la fourchette</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>284 ventes réelles 2023-2025 (DVF)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>DVF = prix réellement payés, enregistrés chez le notaire (data.gouv.fr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>HYPOTHÈSES — cellules jaunes à ajuster avec votre conseiller</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Prix négocié retenu</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B25" s="19" t="n">
         <v>200000</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>par défaut le prix affiché — un prix demandé se négocie</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Frais d'acquisition (notaire, garanties)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B26" s="20" t="n">
         <v>0.08</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Apport personnel</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B27" s="20" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Taux du crédit (hors assurance)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B28" s="20" t="n">
         <v>0.0458</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Durée du crédit (années)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B29" s="21" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Taxe foncière (en mois de loyer par an)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B30" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>à remplacer par le montant réel dès que connu</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Provision entretien &amp; vacance (% du loyer)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
+      <c r="B31" s="20" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Assurance propriétaire (PNO, €/an)</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n">
+      <c r="B32" s="19" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>PLAN DE FINANCEMENT</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Coût d'acquisition total</t>
         </is>
       </c>
-      <c r="B25" s="11">
-        <f>B15*(1+B16)</f>
-        <v/>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="B35" s="17">
+        <f>B25*(1+B26)</f>
+        <v/>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>prix négocié + frais d'acquisition</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Apport personnel</t>
         </is>
       </c>
-      <c r="B26" s="11">
-        <f>B25*B17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="B36" s="17">
+        <f>B35*B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>Montant emprunté</t>
         </is>
       </c>
-      <c r="B27" s="11">
-        <f>B25-B26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="B37" s="17">
+        <f>B35-B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Mensualité du crédit</t>
         </is>
       </c>
-      <c r="B28" s="17">
-        <f>IFERROR(-PMT(B18/12,B19*12,B27),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="B38" s="23">
+        <f>IFERROR(-PMT(B28/12,B29*12,B37),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Service de la dette (annuel)</t>
         </is>
       </c>
-      <c r="B29" s="11">
-        <f>B28*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="B39" s="17">
+        <f>B38*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>EXPLOITATION ANNUELLE</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>Loyers annuels HT</t>
         </is>
       </c>
-      <c r="B32" s="11">
-        <f>IFERROR(B11*12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="B42" s="17">
+        <f>IFERROR(B20*12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>− Taxe foncière</t>
         </is>
       </c>
-      <c r="B33" s="11">
-        <f>-IFERROR(B11*B20,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="B43" s="17">
+        <f>-IFERROR(B20*B30,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>− Entretien &amp; vacance locative</t>
         </is>
       </c>
-      <c r="B34" s="11">
-        <f>-B32*B21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="B44" s="17">
+        <f>-B42*B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>− Assurance PNO</t>
         </is>
       </c>
-      <c r="B35" s="11">
-        <f>-B22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="B45" s="17">
+        <f>-B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>Revenu net avant crédit</t>
         </is>
       </c>
-      <c r="B36" s="11">
-        <f>B32+B33+B34+B35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="B46" s="17">
+        <f>B42+B43+B44+B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>− Remboursement du crédit</t>
         </is>
       </c>
-      <c r="B37" s="11">
-        <f>-B29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="B47" s="17">
+        <f>-B39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>Cash-flow annuel</t>
         </is>
       </c>
-      <c r="B38" s="11">
-        <f>B36-B29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="B48" s="17">
+        <f>B46-B39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>Cash-flow mensuel</t>
         </is>
       </c>
-      <c r="B39" s="18">
-        <f>B38/12</f>
-        <v/>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="B49" s="24">
+        <f>B48/12</f>
+        <v/>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>positif : le bien se paie tout seul, loyer ≥ crédit + charges</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>LES RATIOS QUE REGARDE LE BANQUIER</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Rendement brut</t>
         </is>
       </c>
-      <c r="B42" s="19">
-        <f>IFERROR(B32/B15,"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="B52" s="25">
+        <f>IFERROR(B42/B25,"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Rendement net avant crédit</t>
         </is>
       </c>
-      <c r="B43" s="19">
-        <f>IFERROR(B36/B25,"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="B53" s="25">
+        <f>IFERROR(B46/B35,"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
         <is>
           <t>après taxe foncière, entretien et assurance</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>DSCR — couverture de la dette</t>
         </is>
       </c>
-      <c r="B44" s="20">
-        <f>IFERROR(B36/B29,"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="B54" s="26">
+        <f>IFERROR(B46/B39,"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
         <is>
           <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>LTV — part financée par la banque</t>
         </is>
       </c>
-      <c r="B45" s="19">
-        <f>IFERROR(B27/B15,"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="B55" s="25">
+        <f>IFERROR(B37/B25,"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
         <is>
           <t>≤ 80 % est la zone de confort bancaire</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
         <is>
           <t>Effort d'épargne mensuel si négatif</t>
         </is>
       </c>
-      <c r="B46" s="17">
-        <f>MAX(0,-B38/12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="B56" s="23">
+        <f>MAX(0,-B48/12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>Score de l'outil de veille</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>64/100</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>rendement, emplacement, prix vs marché, proximité</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +826 €/mois.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>rendement, emplacement, prix vs marché, financement, fiscalité</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="27" t="inlineStr">
         <is>
           <t>⚠ AVERTISSEMENT : le rendement affiché par le vendeur est anormalement élevé. Exiger le bail et les quittances avant toute offre — ce dossier reprend le loyer annoncé tel quel.</t>
         </is>
       </c>
     </row>
-    <row r="53"/>
+    <row r="60"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A49:C51"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A52:C53"/>
+    <mergeCell ref="A59:C60"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A13:C14"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A51:C51"/>
   </mergeCells>
-  <conditionalFormatting sqref="B38:B39">
+  <conditionalFormatting sqref="B48">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1327,18 +1435,43 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
+  <conditionalFormatting sqref="B49">
     <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>1.2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 Les Murs. — dossier indicatif généré automatiquement ; l'offre de prêt de la banque fait foi</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
@@ -1361,33 +1494,33 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Année</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>Capital dû en début d'année</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="28" t="inlineStr">
         <is>
           <t>Intérêts de l'année</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="28" t="inlineStr">
         <is>
           <t>Capital remboursé</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="28" t="inlineStr">
         <is>
           <t>Capital restant dû</t>
         </is>
       </c>
       <c r="G1">
-        <f>'Synthèse'!B19</f>
+        <f>'Synthèse'!B29</f>
         <v/>
       </c>
     </row>
@@ -1395,29 +1528,29 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
-        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$27,"")</f>
-        <v/>
-      </c>
-      <c r="C2" s="7">
+      <c r="B2" s="8">
+        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$37,"")</f>
+        <v/>
+      </c>
+      <c r="C2" s="8">
         <f>IF(A2&lt;=$G$1,B2*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <f>IF(A2&lt;=$G$1,MIN(B2,$G$3-C2),"")</f>
         <v/>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>IF(A2&lt;=$G$1,MAX(0,B2-D2),"")</f>
         <v/>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Tableau indicatif (pas annuel) — l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
       <c r="G2">
-        <f>'Synthèse'!B18</f>
+        <f>'Synthèse'!B28</f>
         <v/>
       </c>
     </row>
@@ -1425,24 +1558,24 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="8">
         <f>IF(A3&lt;=$G$1,E2,"")</f>
         <v/>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="8">
         <f>IF(A3&lt;=$G$1,B3*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <f>IF(A3&lt;=$G$1,MIN(B3,$G$3-C3),"")</f>
         <v/>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="8">
         <f>IF(A3&lt;=$G$1,MAX(0,B3-D3),"")</f>
         <v/>
       </c>
       <c r="G3">
-        <f>'Synthèse'!B29</f>
+        <f>'Synthèse'!B39</f>
         <v/>
       </c>
     </row>
@@ -1450,19 +1583,19 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="8">
         <f>IF(A4&lt;=$G$1,E3,"")</f>
         <v/>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="8">
         <f>IF(A4&lt;=$G$1,B4*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="8">
         <f>IF(A4&lt;=$G$1,MIN(B4,$G$3-C4),"")</f>
         <v/>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <f>IF(A4&lt;=$G$1,MAX(0,B4-D4),"")</f>
         <v/>
       </c>
@@ -1471,19 +1604,19 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <f>IF(A5&lt;=$G$1,E4,"")</f>
         <v/>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="8">
         <f>IF(A5&lt;=$G$1,B5*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="8">
         <f>IF(A5&lt;=$G$1,MIN(B5,$G$3-C5),"")</f>
         <v/>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <f>IF(A5&lt;=$G$1,MAX(0,B5-D5),"")</f>
         <v/>
       </c>
@@ -1492,19 +1625,19 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <f>IF(A6&lt;=$G$1,E5,"")</f>
         <v/>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>IF(A6&lt;=$G$1,B6*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>IF(A6&lt;=$G$1,MIN(B6,$G$3-C6),"")</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>IF(A6&lt;=$G$1,MAX(0,B6-D6),"")</f>
         <v/>
       </c>
@@ -1513,19 +1646,19 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <f>IF(A7&lt;=$G$1,E6,"")</f>
         <v/>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <f>IF(A7&lt;=$G$1,B7*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>IF(A7&lt;=$G$1,MIN(B7,$G$3-C7),"")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>IF(A7&lt;=$G$1,MAX(0,B7-D7),"")</f>
         <v/>
       </c>
@@ -1534,19 +1667,19 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="8">
         <f>IF(A8&lt;=$G$1,E7,"")</f>
         <v/>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>IF(A8&lt;=$G$1,B8*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>IF(A8&lt;=$G$1,MIN(B8,$G$3-C8),"")</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>IF(A8&lt;=$G$1,MAX(0,B8-D8),"")</f>
         <v/>
       </c>
@@ -1555,19 +1688,19 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="8">
         <f>IF(A9&lt;=$G$1,E8,"")</f>
         <v/>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <f>IF(A9&lt;=$G$1,B9*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>IF(A9&lt;=$G$1,MIN(B9,$G$3-C9),"")</f>
         <v/>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f>IF(A9&lt;=$G$1,MAX(0,B9-D9),"")</f>
         <v/>
       </c>
@@ -1576,19 +1709,19 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="8">
         <f>IF(A10&lt;=$G$1,E9,"")</f>
         <v/>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <f>IF(A10&lt;=$G$1,B10*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>IF(A10&lt;=$G$1,MIN(B10,$G$3-C10),"")</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>IF(A10&lt;=$G$1,MAX(0,B10-D10),"")</f>
         <v/>
       </c>
@@ -1597,19 +1730,19 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <f>IF(A11&lt;=$G$1,E10,"")</f>
         <v/>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>IF(A11&lt;=$G$1,B11*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>IF(A11&lt;=$G$1,MIN(B11,$G$3-C11),"")</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>IF(A11&lt;=$G$1,MAX(0,B11-D11),"")</f>
         <v/>
       </c>
@@ -1618,19 +1751,19 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <f>IF(A12&lt;=$G$1,E11,"")</f>
         <v/>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <f>IF(A12&lt;=$G$1,B12*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <f>IF(A12&lt;=$G$1,MIN(B12,$G$3-C12),"")</f>
         <v/>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <f>IF(A12&lt;=$G$1,MAX(0,B12-D12),"")</f>
         <v/>
       </c>
@@ -1639,19 +1772,19 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="8">
         <f>IF(A13&lt;=$G$1,E12,"")</f>
         <v/>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <f>IF(A13&lt;=$G$1,B13*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="8">
         <f>IF(A13&lt;=$G$1,MIN(B13,$G$3-C13),"")</f>
         <v/>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="8">
         <f>IF(A13&lt;=$G$1,MAX(0,B13-D13),"")</f>
         <v/>
       </c>
@@ -1660,19 +1793,19 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="8">
         <f>IF(A14&lt;=$G$1,E13,"")</f>
         <v/>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <f>IF(A14&lt;=$G$1,B14*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="8">
         <f>IF(A14&lt;=$G$1,MIN(B14,$G$3-C14),"")</f>
         <v/>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="8">
         <f>IF(A14&lt;=$G$1,MAX(0,B14-D14),"")</f>
         <v/>
       </c>
@@ -1681,19 +1814,19 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <f>IF(A15&lt;=$G$1,E14,"")</f>
         <v/>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <f>IF(A15&lt;=$G$1,B15*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="8">
         <f>IF(A15&lt;=$G$1,MIN(B15,$G$3-C15),"")</f>
         <v/>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="8">
         <f>IF(A15&lt;=$G$1,MAX(0,B15-D15),"")</f>
         <v/>
       </c>
@@ -1702,19 +1835,19 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <f>IF(A16&lt;=$G$1,E15,"")</f>
         <v/>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <f>IF(A16&lt;=$G$1,B16*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <f>IF(A16&lt;=$G$1,MIN(B16,$G$3-C16),"")</f>
         <v/>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <f>IF(A16&lt;=$G$1,MAX(0,B16-D16),"")</f>
         <v/>
       </c>
@@ -1723,19 +1856,19 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <f>IF(A17&lt;=$G$1,E16,"")</f>
         <v/>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <f>IF(A17&lt;=$G$1,B17*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <f>IF(A17&lt;=$G$1,MIN(B17,$G$3-C17),"")</f>
         <v/>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <f>IF(A17&lt;=$G$1,MAX(0,B17-D17),"")</f>
         <v/>
       </c>
@@ -1744,19 +1877,19 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="8">
         <f>IF(A18&lt;=$G$1,E17,"")</f>
         <v/>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <f>IF(A18&lt;=$G$1,B18*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <f>IF(A18&lt;=$G$1,MIN(B18,$G$3-C18),"")</f>
         <v/>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <f>IF(A18&lt;=$G$1,MAX(0,B18-D18),"")</f>
         <v/>
       </c>
@@ -1765,19 +1898,19 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <f>IF(A19&lt;=$G$1,E18,"")</f>
         <v/>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <f>IF(A19&lt;=$G$1,B19*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <f>IF(A19&lt;=$G$1,MIN(B19,$G$3-C19),"")</f>
         <v/>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <f>IF(A19&lt;=$G$1,MAX(0,B19-D19),"")</f>
         <v/>
       </c>
@@ -1786,19 +1919,19 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="8">
         <f>IF(A20&lt;=$G$1,E19,"")</f>
         <v/>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <f>IF(A20&lt;=$G$1,B20*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <f>IF(A20&lt;=$G$1,MIN(B20,$G$3-C20),"")</f>
         <v/>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <f>IF(A20&lt;=$G$1,MAX(0,B20-D20),"")</f>
         <v/>
       </c>
@@ -1807,19 +1940,19 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="8">
         <f>IF(A21&lt;=$G$1,E20,"")</f>
         <v/>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <f>IF(A21&lt;=$G$1,B21*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="8">
         <f>IF(A21&lt;=$G$1,MIN(B21,$G$3-C21),"")</f>
         <v/>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <f>IF(A21&lt;=$G$1,MAX(0,B21-D21),"")</f>
         <v/>
       </c>
@@ -1828,19 +1961,19 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="8">
         <f>IF(A22&lt;=$G$1,E21,"")</f>
         <v/>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <f>IF(A22&lt;=$G$1,B22*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="8">
         <f>IF(A22&lt;=$G$1,MIN(B22,$G$3-C22),"")</f>
         <v/>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="8">
         <f>IF(A22&lt;=$G$1,MAX(0,B22-D22),"")</f>
         <v/>
       </c>
@@ -1849,19 +1982,19 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="8">
         <f>IF(A23&lt;=$G$1,E22,"")</f>
         <v/>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <f>IF(A23&lt;=$G$1,B23*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="8">
         <f>IF(A23&lt;=$G$1,MIN(B23,$G$3-C23),"")</f>
         <v/>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="8">
         <f>IF(A23&lt;=$G$1,MAX(0,B23-D23),"")</f>
         <v/>
       </c>
@@ -1870,19 +2003,19 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="8">
         <f>IF(A24&lt;=$G$1,E23,"")</f>
         <v/>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="8">
         <f>IF(A24&lt;=$G$1,B24*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="8">
         <f>IF(A24&lt;=$G$1,MIN(B24,$G$3-C24),"")</f>
         <v/>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="8">
         <f>IF(A24&lt;=$G$1,MAX(0,B24-D24),"")</f>
         <v/>
       </c>
@@ -1891,19 +2024,19 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="8">
         <f>IF(A25&lt;=$G$1,E24,"")</f>
         <v/>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="8">
         <f>IF(A25&lt;=$G$1,B25*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="8">
         <f>IF(A25&lt;=$G$1,MIN(B25,$G$3-C25),"")</f>
         <v/>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="8">
         <f>IF(A25&lt;=$G$1,MAX(0,B25-D25),"")</f>
         <v/>
       </c>
@@ -1912,19 +2045,19 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="8">
         <f>IF(A26&lt;=$G$1,E25,"")</f>
         <v/>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="8">
         <f>IF(A26&lt;=$G$1,B26*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="8">
         <f>IF(A26&lt;=$G$1,MIN(B26,$G$3-C26),"")</f>
         <v/>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="8">
         <f>IF(A26&lt;=$G$1,MAX(0,B26-D26),"")</f>
         <v/>
       </c>
@@ -1933,19 +2066,19 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="8">
         <f>IF(A27&lt;=$G$1,E26,"")</f>
         <v/>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <f>IF(A27&lt;=$G$1,B27*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="8">
         <f>IF(A27&lt;=$G$1,MIN(B27,$G$3-C27),"")</f>
         <v/>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="8">
         <f>IF(A27&lt;=$G$1,MAX(0,B27-D27),"")</f>
         <v/>
       </c>
@@ -1954,19 +2087,19 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="8">
         <f>IF(A28&lt;=$G$1,E27,"")</f>
         <v/>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="8">
         <f>IF(A28&lt;=$G$1,B28*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="8">
         <f>IF(A28&lt;=$G$1,MIN(B28,$G$3-C28),"")</f>
         <v/>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="8">
         <f>IF(A28&lt;=$G$1,MAX(0,B28-D28),"")</f>
         <v/>
       </c>
@@ -1975,19 +2108,19 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="8">
         <f>IF(A29&lt;=$G$1,E28,"")</f>
         <v/>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="8">
         <f>IF(A29&lt;=$G$1,B29*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="8">
         <f>IF(A29&lt;=$G$1,MIN(B29,$G$3-C29),"")</f>
         <v/>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="8">
         <f>IF(A29&lt;=$G$1,MAX(0,B29-D29),"")</f>
         <v/>
       </c>
@@ -1996,19 +2129,19 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="8">
         <f>IF(A30&lt;=$G$1,E29,"")</f>
         <v/>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="8">
         <f>IF(A30&lt;=$G$1,B30*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="8">
         <f>IF(A30&lt;=$G$1,MIN(B30,$G$3-C30),"")</f>
         <v/>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="8">
         <f>IF(A30&lt;=$G$1,MAX(0,B30-D30),"")</f>
         <v/>
       </c>
@@ -2017,19 +2150,19 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="8">
         <f>IF(A31&lt;=$G$1,E30,"")</f>
         <v/>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="8">
         <f>IF(A31&lt;=$G$1,B31*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="8">
         <f>IF(A31&lt;=$G$1,MIN(B31,$G$3-C31),"")</f>
         <v/>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="8">
         <f>IF(A31&lt;=$G$1,MAX(0,B31-D31),"")</f>
         <v/>
       </c>
@@ -2046,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2054,120 +2187,144 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Titre</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Vente Local commercial 44m² Paris</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Lien</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>https://www.cessionpme.com/annonce,immo-entreprise-vente-local-commercial-boutique-paris-6e-75006,2750109,A,offre.html</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Ville</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>Paris 6e (75006)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>cessionpme</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Première détection</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Murs libres</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Caractéristiques</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Extraction / vraie restauration possible · Terrasse</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Évolution du prix</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>stable depuis la première vue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Fourchette de marché</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>284 ventes réelles 2023-2025 (DVF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Lecture du prix</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Décote sans explication visible dans l'annonce : possible bonne affaire — ou défaut caché (état, copropriété, bail) à vérifier sur place.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Alertes</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>loyer_estime · rendement_anormalement_eleve</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+    <row r="12" ht="110" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Notre équipe vous propose un restaurant 75006 d'une capacité de 24 couverts et une cuisine de plain pieds avec extraction de 400 tenu depuis 13 ans par un cuisinier japonais réalisant une cuisine bistrotière. Affaire clé en mains le matériel est récent et bien entretenu. Terrasse éphémère de 14 places. Le CA annuel moyen sur les trois dernières années est de 255K euros .Loyer de 2252 euros ttc cc /mois. Prix de cession 200K euros net vendeur. Fermeture dimanche et lundi midi. Disponibilité : Immédiate Bus Maine - Vaugirard (28, 82, 89, 92), Duroc (86), Vaneau - Saint-Romain (70) Métro Duroc (1</t>
         </is>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +826 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +889 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +889 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +826 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +826 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +810 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +810 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +796 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-6e-a478101c.xlsx
+++ b/docs/dossiers/dossier-paris-6e-a478101c.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
